--- a/adresses.xlsx
+++ b/adresses.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="142">
   <si>
     <t>Адрес объекта</t>
   </si>
@@ -25,36 +25,162 @@
     <t>Округ</t>
   </si>
   <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 31</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Захарьинские Дворики, дом 3</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 21</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, Типографская улица, дом 2</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 8</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 22, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 28</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, Типографская улица, дом 6</t>
+  </si>
+  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 12, корпус 1</t>
   </si>
   <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 7</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, Типографская улица, дом 14</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 18, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 30</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 11</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 27</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 9</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 32, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 32</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 4, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 17</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 35, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 20, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 8, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 6, корпус 3</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 18, корпус 2</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 26</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 16, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 39, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 24, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 27, корпус 3</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 37, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, Дачная улица, дом 4</t>
+  </si>
+  <si>
+    <t>Типографская ул. 24</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 30, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, Дачная улица, дом 7</t>
+  </si>
+  <si>
+    <t>Брусилова улица</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Захарьинские Дворики, дом 1, корпус 2</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 27, корпус 2</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 18</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 24</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, Дачная улица, дом 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 33, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 6, корпус 1</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 4, корпус 2</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 16</t>
+  </si>
+  <si>
+    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 27, корпус 1</t>
+  </si>
+  <si>
+    <t>парк на ул Брусилова</t>
+  </si>
+  <si>
+    <t>Савицкого Маршала ул. 8</t>
+  </si>
+  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 15</t>
   </si>
   <si>
-    <t>Типографская ул. 24</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Захарьинские Дворики, дом 3</t>
-  </si>
-  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Захарьинские Дворики, дом 1, корпус 1</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 6, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 35, корпус 1</t>
-  </si>
-  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 26, корпус 2</t>
   </si>
   <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 20</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 16, корпус 1</t>
-  </si>
-  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 15, корпус 1</t>
   </si>
   <si>
@@ -64,102 +190,30 @@
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 22</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 17</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 8</t>
-  </si>
-  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 22, корпус 2</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 21</t>
-  </si>
-  <si>
     <t>Брусилова ул. 11</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 11</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 4, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, Типографская улица, дом 14</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 31</t>
-  </si>
-  <si>
     <t>Захарьинские Дворики ул. 3 к.1</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 20, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 24</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 18, корпус 2</t>
-  </si>
-  <si>
     <t>Брусилова ул. 33 к.1</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Захарьинские Дворики, дом 1, корпус 2</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 24, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 8, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 22, корпус 1</t>
-  </si>
-  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, Дачная улица, дом 3</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 37, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 33, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 39, корпус 1</t>
-  </si>
-  <si>
     <t>Брусилова ул. 27</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 18, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 27, корпус 3</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 27, корпус 2</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 16</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 27</t>
-  </si>
-  <si>
     <t>Савицкого Маршала ул. 22 к.1</t>
   </si>
   <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Захарьинские Дворики, дом 3, корпус 1</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 6, корпус 3</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 27, корпус 1</t>
-  </si>
-  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 13</t>
   </si>
   <si>
@@ -169,24 +223,12 @@
     <t>Савицкого Маршала ул. 24</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 4, корпус 2</t>
-  </si>
-  <si>
     <t>Дачная улица 3</t>
   </si>
   <si>
     <t>Савицкого Маршала ул. 16</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, Типографская улица, дом 6</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, Типографская улица, дом 2</t>
-  </si>
-  <si>
-    <t>парк на ул Брусилова</t>
-  </si>
-  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, Типографская улица, дом 24</t>
   </si>
   <si>
@@ -202,9 +244,6 @@
     <t>Николая Сироткина улица</t>
   </si>
   <si>
-    <t>Брусилова улица</t>
-  </si>
-  <si>
     <t>Маршала Савицкого улица</t>
   </si>
   <si>
@@ -214,24 +253,9 @@
     <t>Савицкого Маршала ул. 12</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 7</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 26</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 32</t>
-  </si>
-  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 28, корпус 1</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 30</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Брусилова, дом 9</t>
-  </si>
-  <si>
     <t>Захарьинские Дворики ул. 1 к.1</t>
   </si>
   <si>
@@ -256,18 +280,6 @@
     <t>Савицкого Маршала ул. 26 к.1</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 30, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 32, корпус 1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 28</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Маршала Савицкого, дом 18</t>
-  </si>
-  <si>
     <t>Захарьинские Дворики улица</t>
   </si>
   <si>
@@ -277,24 +289,15 @@
     <t>Савицкого Маршала ул. 22 к.2</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, Дачная улица, дом 7</t>
-  </si>
-  <si>
     <t>внутригородская территория муниципальный округ Южное Бутово, улица Николая Сироткина, дом 2, корпус 1</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, Дачная улица, дом 4</t>
-  </si>
-  <si>
     <t>Савицкого Маршала ул. 30 к.1</t>
   </si>
   <si>
     <t>Савицкого Маршала ул. 28</t>
   </si>
   <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, Дачная улица, дом 1</t>
-  </si>
-  <si>
     <t>Типографская ул. 2</t>
   </si>
   <si>
@@ -349,9 +352,6 @@
     <t>Савицкого Маршала ул. 22</t>
   </si>
   <si>
-    <t>Савицкого Маршала ул. 8</t>
-  </si>
-  <si>
     <t>Савицкого Маршала ул. 6 к.3</t>
   </si>
   <si>
@@ -376,88 +376,58 @@
     <t>Савицкого Маршала ул. 4 к.1</t>
   </si>
   <si>
+    <t>Брусилова ул. 37 к.1</t>
+  </si>
+  <si>
+    <t>Брусилова ул. 31</t>
+  </si>
+  <si>
+    <t>Савицкого Маршала ул. 32 к.1</t>
+  </si>
+  <si>
+    <t>Брусилова ул. 39 к.1</t>
+  </si>
+  <si>
+    <t>Типографская улица</t>
+  </si>
+  <si>
+    <t>Савицкого Маршала ул. 4 к.2</t>
+  </si>
+  <si>
+    <t>Савицкого Маршала ул. 28 к.1</t>
+  </si>
+  <si>
+    <t>Дачная улица 2</t>
+  </si>
+  <si>
     <t>Дачная улица 7</t>
   </si>
   <si>
-    <t>Брусилова ул. 7</t>
-  </si>
-  <si>
-    <t>Дачная улица 2</t>
-  </si>
-  <si>
-    <t>Савицкого Маршала ул. 4 к.2</t>
-  </si>
-  <si>
-    <t>Дачная ул. (Щербинка) 1</t>
+    <t>Парк «Брусилова вблизи дома 27».</t>
+  </si>
+  <si>
+    <t>Дачная улица 4</t>
+  </si>
+  <si>
+    <t>Савицкого Маршала ул. 6 к.1</t>
+  </si>
+  <si>
+    <t>Парк «Брусилова».</t>
   </si>
   <si>
     <t>Савицкого Маршала ул. 26 к.2</t>
   </si>
   <si>
+    <t>Проезд от улицы Дачная до автобазы</t>
+  </si>
+  <si>
+    <t>Проезд от Обводной дороги до улицы Брусилова</t>
+  </si>
+  <si>
+    <t>Савицкого Маршала ул. 20</t>
+  </si>
+  <si>
     <t>Брусилова ул. 27 к.3</t>
-  </si>
-  <si>
-    <t>Варшавское шоссе-эстакада на пересечении с улицей Маршала Савицкого</t>
-  </si>
-  <si>
-    <t>Савицкого Маршала ул. 24 к.1</t>
-  </si>
-  <si>
-    <t>Савицкого Маршала ул. 6 к.1</t>
-  </si>
-  <si>
-    <t>Савицкого Маршала ул. 20</t>
-  </si>
-  <si>
-    <t>Дачная улица 4</t>
-  </si>
-  <si>
-    <t>Типографская улица</t>
-  </si>
-  <si>
-    <t>Брусилова ул. 39 к.1</t>
-  </si>
-  <si>
-    <t>Савицкого Маршала ул. 28 к.1</t>
-  </si>
-  <si>
-    <t>Брусилова ул. 31</t>
-  </si>
-  <si>
-    <t>Проезд от улицы Дачная до автобазы</t>
-  </si>
-  <si>
-    <t>Савицкого Маршала ул. 32 к.1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Николая Сироткина, домовладение 2, корпус 1</t>
-  </si>
-  <si>
-    <t>Савицкого Маршала ул. 18 к.1</t>
-  </si>
-  <si>
-    <t>Савицкого Маршала ул. 8 к.1</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Николая Сироткина, дом 2, корпус 3</t>
-  </si>
-  <si>
-    <t>Брусилова ул. 37 к.1</t>
-  </si>
-  <si>
-    <t>Савицкого Маршала ул. 18</t>
-  </si>
-  <si>
-    <t>внутригородская территория муниципальный округ Южное Бутово, улица Николая Сироткина, домовладение 2, корпус 4</t>
-  </si>
-  <si>
-    <t>Проезд от Обводной дороги до улицы Брусилова</t>
-  </si>
-  <si>
-    <t>Проезд Типографская улица, д.2А</t>
-  </si>
-  <si>
-    <t>Парк «Брусилова вблизи дома 27».</t>
   </si>
   <si>
     <t>Южное Бутово</t>
@@ -827,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -846,10 +816,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -857,10 +827,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -868,10 +838,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -879,10 +849,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -890,10 +860,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -901,10 +871,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -912,10 +882,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -923,10 +893,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -934,10 +904,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -945,10 +915,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -956,10 +926,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -967,10 +937,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -978,10 +948,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -989,10 +959,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1000,10 +970,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1011,10 +981,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1022,10 +992,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1033,10 +1003,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1044,10 +1014,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1055,10 +1025,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1066,10 +1036,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C22" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1077,10 +1047,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1088,10 +1058,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1099,10 +1069,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1110,10 +1080,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1121,10 +1091,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1132,10 +1102,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1143,10 +1113,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C29" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1154,10 +1124,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1165,10 +1135,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1176,10 +1146,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1187,10 +1157,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1198,10 +1168,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1209,10 +1179,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1220,10 +1190,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1231,10 +1201,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1242,10 +1212,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C38" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1253,10 +1223,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1264,10 +1234,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1275,10 +1245,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1286,10 +1256,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1297,10 +1267,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1308,10 +1278,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1319,10 +1289,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1330,10 +1300,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1341,10 +1311,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1352,10 +1322,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1363,10 +1333,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C49" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1374,10 +1344,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1385,10 +1355,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C51" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1396,10 +1366,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1407,10 +1377,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C53" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1418,10 +1388,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1429,10 +1399,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1440,10 +1410,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C56" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1451,10 +1421,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C57" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1462,10 +1432,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1473,10 +1443,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C59" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1484,10 +1454,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C60" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1495,10 +1465,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1506,10 +1476,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C62" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1517,10 +1487,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C63" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1528,10 +1498,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C64" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1539,10 +1509,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1550,10 +1520,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1561,10 +1531,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1572,10 +1542,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C68" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1583,10 +1553,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1594,10 +1564,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C70" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1605,10 +1575,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C71" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1616,10 +1586,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C72" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1627,10 +1597,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C73" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1638,10 +1608,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C74" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1649,10 +1619,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C75" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1660,10 +1630,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C76" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1671,10 +1641,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C77" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1682,10 +1652,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1693,10 +1663,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C79" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1704,10 +1674,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C80" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1715,10 +1685,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C81" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1726,10 +1696,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C82" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1737,10 +1707,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C83" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1748,10 +1718,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C84" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1759,10 +1729,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C85" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1770,10 +1740,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C86" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1781,10 +1751,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C87" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1792,10 +1762,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C88" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1803,10 +1773,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C89" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1814,10 +1784,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C90" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1825,10 +1795,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1836,10 +1806,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C92" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1847,10 +1817,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C93" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1858,10 +1828,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C94" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1869,10 +1839,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1880,10 +1850,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C96" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1891,10 +1861,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C97" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1902,10 +1872,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C98" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1913,10 +1883,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C99" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1924,10 +1894,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C100" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1935,10 +1905,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C101" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1946,10 +1916,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C102" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1957,10 +1927,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C103" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1968,10 +1938,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C104" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1979,10 +1949,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C105" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1990,10 +1960,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C106" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2001,10 +1971,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C107" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2012,10 +1982,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C108" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2023,10 +1993,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C109" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2034,10 +2004,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C110" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2045,10 +2015,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C111" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2056,10 +2026,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C112" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2067,10 +2037,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C113" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2078,10 +2048,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C114" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2089,10 +2059,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C115" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2100,10 +2070,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2111,10 +2081,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C117" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2122,10 +2092,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C118" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2133,10 +2103,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C119" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2144,10 +2114,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C120" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2155,10 +2125,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C121" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2166,10 +2136,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C122" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2177,10 +2147,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C123" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2188,10 +2158,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C124" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2199,10 +2169,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C125" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2210,10 +2180,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C126" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2221,10 +2191,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C127" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2232,10 +2202,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C128" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2243,10 +2213,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C129" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2254,10 +2224,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2265,10 +2235,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C131" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2276,10 +2246,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C132" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2287,10 +2257,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C133" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2298,10 +2268,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2309,10 +2279,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2320,120 +2290,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C136" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" t="s">
-        <v>138</v>
-      </c>
-      <c r="B137" t="s">
-        <v>148</v>
-      </c>
-      <c r="C137" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" t="s">
-        <v>139</v>
-      </c>
-      <c r="B138" t="s">
-        <v>149</v>
-      </c>
-      <c r="C138" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" t="s">
-        <v>140</v>
-      </c>
-      <c r="B139" t="s">
-        <v>149</v>
-      </c>
-      <c r="C139" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" t="s">
-        <v>141</v>
-      </c>
-      <c r="B140" t="s">
-        <v>148</v>
-      </c>
-      <c r="C140" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" t="s">
-        <v>142</v>
-      </c>
-      <c r="B141" t="s">
-        <v>149</v>
-      </c>
-      <c r="C141" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" t="s">
-        <v>143</v>
-      </c>
-      <c r="B142" t="s">
-        <v>149</v>
-      </c>
-      <c r="C142" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143" t="s">
-        <v>144</v>
-      </c>
-      <c r="B143" t="s">
-        <v>148</v>
-      </c>
-      <c r="C143" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" t="s">
-        <v>145</v>
-      </c>
-      <c r="B144" t="s">
-        <v>149</v>
-      </c>
-      <c r="C144" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" t="s">
-        <v>146</v>
-      </c>
-      <c r="B145" t="s">
-        <v>149</v>
-      </c>
-      <c r="C145" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" t="s">
-        <v>147</v>
-      </c>
-      <c r="B146" t="s">
-        <v>149</v>
-      </c>
-      <c r="C146" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
